--- a/docs/downloads/04/tbl_other_educ_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -388,10 +388,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D2">
-        <v>37.2</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="3">
@@ -438,32 +438,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="D6">
-        <v>0.6</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="7">
@@ -474,14 +474,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C7">
-        <v>129</v>
+        <v>190</v>
       </c>
       <c r="D7">
-        <v>31.3</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="8">
@@ -492,14 +492,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C8">
-        <v>190</v>
+        <v>67</v>
       </c>
       <c r="D8">
-        <v>46.1</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="9">
@@ -510,50 +510,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C9">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D9">
-        <v>16.3</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="D10">
-        <v>5.3</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>187</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="12">
@@ -564,14 +564,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C12">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="D12">
-        <v>39</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="13">
@@ -582,50 +582,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C13">
-        <v>187</v>
+        <v>16</v>
       </c>
       <c r="D13">
-        <v>47.7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C14">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="D14">
-        <v>11.7</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>223</v>
       </c>
       <c r="D15">
-        <v>1.5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
@@ -636,14 +636,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C16">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="D16">
-        <v>28.7</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="17">
@@ -654,68 +654,68 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C17">
-        <v>223</v>
+        <v>24</v>
       </c>
       <c r="D17">
-        <v>52</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C18">
-        <v>70</v>
+        <v>554</v>
       </c>
       <c r="D18">
-        <v>16.3</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>854</v>
       </c>
       <c r="D19">
-        <v>2.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Universitaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>256</v>
       </c>
       <c r="D20">
-        <v>0.7</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="21">
@@ -726,86 +726,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C21">
-        <v>608</v>
+        <v>114</v>
       </c>
       <c r="D21">
-        <v>34.2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>854</v>
-      </c>
-      <c r="D22">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Secondaire 1er cycle</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>256</v>
-      </c>
-      <c r="D23">
-        <v>14.4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>50</v>
-      </c>
-      <c r="D24">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>10</v>
-      </c>
-      <c r="D25">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_other_educ_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -388,10 +388,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>189</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>34.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
@@ -402,14 +402,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C3">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="D3">
-        <v>46.6</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="4">
@@ -420,14 +420,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C4">
-        <v>73</v>
+        <v>254</v>
       </c>
       <c r="D4">
-        <v>13.4</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="5">
@@ -438,32 +438,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="D5">
-        <v>5.3</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C6">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>26.7</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="7">
@@ -474,14 +474,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C7">
-        <v>190</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>46.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -492,14 +492,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C8">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="D8">
-        <v>16.3</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="9">
@@ -510,50 +510,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C9">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="D9">
-        <v>10.9</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C10">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="D10">
-        <v>36.5</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C11">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="D11">
-        <v>47.7</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="12">
@@ -564,14 +564,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C12">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D12">
-        <v>11.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="13">
@@ -582,68 +582,68 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C13">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="D13">
-        <v>4.1</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="C14">
-        <v>112</v>
+        <v>187</v>
       </c>
       <c r="D14">
-        <v>26.1</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 1er cycle</t>
         </is>
       </c>
       <c r="C15">
-        <v>223</v>
+        <v>46</v>
       </c>
       <c r="D15">
-        <v>52</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Secondaire 1er cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="C16">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="D16">
-        <v>16.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="17">
@@ -654,38 +654,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle &amp; sup.</t>
+          <t>Inconnu</t>
         </is>
       </c>
       <c r="C17">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D17">
-        <v>5.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Non scolarisé</t>
         </is>
       </c>
       <c r="C18">
-        <v>554</v>
+        <v>95</v>
       </c>
       <c r="D18">
-        <v>31.2</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -694,16 +694,16 @@
         </is>
       </c>
       <c r="C19">
-        <v>854</v>
+        <v>223</v>
       </c>
       <c r="D19">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -712,27 +712,117 @@
         </is>
       </c>
       <c r="C20">
-        <v>256</v>
+        <v>70</v>
       </c>
       <c r="D20">
-        <v>14.4</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Marovoay - Maroala</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>24</v>
+      </c>
+      <c r="D21">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Marovoay - Tous</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>67</v>
+      </c>
+      <c r="D22">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Non scolarisé</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>487</v>
+      </c>
+      <c r="D23">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Primaire</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>854</v>
+      </c>
+      <c r="D24">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Secondaire 1er cycle</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>256</v>
+      </c>
+      <c r="D25">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
-      <c r="C21">
+      <c r="C26">
         <v>114</v>
       </c>
-      <c r="D21">
+      <c r="D26">
         <v>6.4</v>
       </c>
     </row>

--- a/docs/downloads/04/tbl_other_educ_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_educ_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
